--- a/r5-TC-FHIR-AG-Scheduling-R5-5-add-fsh-profiles-and-value-set-service-type/StructureDefinition-at-scheduling-appointmentresponse.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-5-add-fsh-profiles-and-value-set-service-type/StructureDefinition-at-scheduling-appointmentresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T10:12:02+00:00</t>
+    <t>2025-01-28T14:00:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -498,7 +498,7 @@
     <t>AppointmentResponse.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Appointment)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-appointment)
 </t>
   </si>
   <si>
@@ -612,7 +612,7 @@
     <t>AppointmentResponse.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Practitioner|PractitionerRole|RelatedPerson|Device|HealthcareService|Location)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-patient|Group|http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-practitionerRole|RelatedPerson|Device|http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-healthcareservice|Location)
 </t>
   </si>
   <si>
@@ -1034,7 +1034,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="97.6328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
